--- a/data/trans_orig/P43E-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P43E-Edad-trans_orig.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W28"/>
+  <dimension ref="A1:P28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -525,25 +525,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el lugar donde le realizaron dicha citología vaginal en 2012</t>
+          <t>Población según si era asistencia pública o privada donde le realizaron la última citología vaginal en 2012 (tasa de respuesta: 98,1%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +547,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -563,17 +556,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -644,41 +626,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -701,13 +648,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -722,37 +662,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>35</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>36356</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>26173</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>47987</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +707,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26157</t>
+          <t>26173</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47550</t>
+          <t>47987</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,47 +722,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>36356</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>26157</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>47550</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>21,85%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>15,72%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>28,57%</t>
+          <t>28,84%</t>
         </is>
       </c>
     </row>
@@ -835,37 +740,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>124</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>130057</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>118426</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>140240</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +785,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>118863</t>
+          <t>118426</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>140256</t>
+          <t>140240</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,47 +800,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>130057</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>118863</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>140256</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>78,15%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>71,43%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>84,28%</t>
+          <t>84,27%</t>
         </is>
       </c>
     </row>
@@ -948,37 +818,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>159</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>166413</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>166413</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>166413</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1012,41 +882,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>166413</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>166413</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>166413</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1065,37 +900,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>109</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>118599</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>100056</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>138245</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +945,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>100764</t>
+          <t>100056</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>137619</t>
+          <t>138245</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,47 +960,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>118599</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>100764</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>137619</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>26,87%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>22,83%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>31,18%</t>
+          <t>31,32%</t>
         </is>
       </c>
     </row>
@@ -1178,37 +978,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>303</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>322754</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>303108</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>341297</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>68,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1023,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>303734</t>
+          <t>303108</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>340589</t>
+          <t>341297</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,47 +1038,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>68,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>303</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>322754</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>303734</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>340589</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>73,13%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>68,82%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>77,17%</t>
+          <t>77,33%</t>
         </is>
       </c>
     </row>
@@ -1291,37 +1056,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>412</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>441353</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>441353</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>441353</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1355,41 +1120,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>412</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>441353</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>441353</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>441353</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1408,37 +1138,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>140</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>150513</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>129239</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>174061</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1183,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>129275</t>
+          <t>129239</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>171139</t>
+          <t>174061</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,42 +1203,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>150513</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>129275</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>171139</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>26,46%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>22,72%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>30,08%</t>
+          <t>30,59%</t>
         </is>
       </c>
     </row>
@@ -1521,37 +1216,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>394</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>418417</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>394869</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>439691</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>73,54%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>69,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1261,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>397791</t>
+          <t>394869</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>439655</t>
+          <t>439691</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,45 +1276,10 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>69,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>77,28%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>394</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>418417</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>397791</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>439655</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>73,54%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>69,92%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
         <is>
           <t>77,28%</t>
         </is>
@@ -1634,37 +1294,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>534</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>568930</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>568930</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>568930</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1698,41 +1358,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>534</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>568930</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>568930</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>568930</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1751,37 +1376,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>117352</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>95205</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>139547</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1421,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>97747</t>
+          <t>95205</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>139465</t>
+          <t>139547</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,47 +1436,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>117352</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>97747</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>139465</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>24,32%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>20,25%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>28,9%</t>
+          <t>28,92%</t>
         </is>
       </c>
     </row>
@@ -1864,37 +1454,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>322</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>365235</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>343040</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>387382</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>71,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1499,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>343122</t>
+          <t>343040</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>384840</t>
+          <t>387382</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,47 +1514,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>71,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>365235</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>343122</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>384840</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>75,68%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>71,1%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>79,75%</t>
+          <t>80,27%</t>
         </is>
       </c>
     </row>
@@ -1977,37 +1532,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>419</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>482587</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>482587</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>482587</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2041,41 +1596,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>419</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>482587</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>482587</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>482587</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2094,37 +1614,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>58247</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>44868</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>75543</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +1659,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>44091</t>
+          <t>44868</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>75923</t>
+          <t>75543</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,47 +1674,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>58247</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>44091</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>75923</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>18,78%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>14,22%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>24,48%</t>
+          <t>24,36%</t>
         </is>
       </c>
     </row>
@@ -2207,37 +1692,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>232</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>251840</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>234544</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>265219</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +1737,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>234164</t>
+          <t>234544</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>265996</t>
+          <t>265219</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,47 +1752,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>251840</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>234164</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>265996</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>81,22%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>75,52%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>85,78%</t>
+          <t>85,53%</t>
         </is>
       </c>
     </row>
@@ -2320,37 +1770,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>280</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>310087</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>310087</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>310087</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2384,41 +1834,6 @@
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>310087</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>310087</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>310087</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2437,37 +1852,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>22039</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14004</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>32251</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +1897,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14055</t>
+          <t>14004</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>32694</t>
+          <t>32251</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,47 +1912,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>22039</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>14055</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>32694</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>12,38%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>7,9%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>18,37%</t>
+          <t>18,12%</t>
         </is>
       </c>
     </row>
@@ -2550,37 +1930,37 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>152</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>155969</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>145757</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>164004</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,62%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +1975,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>145314</t>
+          <t>145757</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>163953</t>
+          <t>164004</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,47 +1990,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>155969</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>145314</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>163953</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>87,62%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>81,63%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>92,1%</t>
+          <t>92,13%</t>
         </is>
       </c>
     </row>
@@ -2663,37 +2008,37 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>172</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>178008</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>178008</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>178008</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2727,41 +2072,6 @@
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>178008</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>178008</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>178008</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2780,37 +2090,37 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14309</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7856</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>22734</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2135,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7953</t>
+          <t>7856</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23340</t>
+          <t>22734</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,47 +2150,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>14309</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>7953</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>23340</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>14,08%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>7,82%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>22,96%</t>
+          <t>22,37%</t>
         </is>
       </c>
     </row>
@@ -2893,37 +2168,37 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>87338</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>78913</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>93791</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2213,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>78307</t>
+          <t>78913</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>93694</t>
+          <t>93791</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,47 +2228,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>87338</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>78307</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>93694</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>85,92%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>77,04%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>92,18%</t>
+          <t>92,27%</t>
         </is>
       </c>
     </row>
@@ -3006,37 +2246,37 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>91</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>101647</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>101647</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>101647</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3070,41 +2310,6 @@
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>101647</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>101647</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>101647</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3123,37 +2328,37 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>461</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>517415</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>474104</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>558644</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +2373,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>477118</t>
+          <t>474104</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>563259</t>
+          <t>558644</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,47 +2388,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>461</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>517415</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>477118</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>563259</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>23,01%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>21,21%</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>25,04%</t>
+          <t>24,84%</t>
         </is>
       </c>
     </row>
@@ -3236,37 +2406,37 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1606</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1731610</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1690381</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1774921</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>75,16%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,92%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +2451,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1685766</t>
+          <t>1690381</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1771907</t>
+          <t>1774921</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,47 +2466,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>75,16%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>1606</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>1731610</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>1685766</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>1771907</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>76,99%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>74,96%</t>
-        </is>
-      </c>
-      <c r="W26" s="2" t="inlineStr">
-        <is>
-          <t>78,79%</t>
+          <t>78,92%</t>
         </is>
       </c>
     </row>
@@ -3349,37 +2484,37 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2067</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2249025</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2249025</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2249025</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3413,41 +2548,6 @@
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>2067</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>2249025</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>2249025</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t>2249025</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W27" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3461,7 +2561,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="11">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -3470,7 +2570,6 @@
     <mergeCell ref="A25:A27"/>
     <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
@@ -3485,7 +2584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W28"/>
+  <dimension ref="A1:P28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3504,25 +2603,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el lugar donde le realizaron dicha citología vaginal en 2016</t>
+          <t>Población según si era asistencia pública o privada donde le realizaron la última citología vaginal en 2016 (tasa de respuesta: 96,09%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3533,7 +2625,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3542,17 +2634,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -3623,41 +2704,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -3680,13 +2726,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -3701,37 +2740,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>25068</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>17379</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>35268</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3746,12 +2785,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17406</t>
+          <t>17379</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35360</t>
+          <t>35268</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3761,47 +2800,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>25068</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>17406</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>35360</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>15,65%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>10,87%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>22,08%</t>
+          <t>22,02%</t>
         </is>
       </c>
     </row>
@@ -3814,37 +2818,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>138</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>135091</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>124891</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>142780</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3859,12 +2863,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>124799</t>
+          <t>124891</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>142753</t>
+          <t>142780</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3874,47 +2878,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>135091</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>124799</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>142753</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>84,35%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>77,92%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>89,13%</t>
+          <t>89,15%</t>
         </is>
       </c>
     </row>
@@ -3927,37 +2896,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>163</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>160159</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>160159</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>160159</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3991,41 +2960,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>160159</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>160159</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>160159</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4044,37 +2978,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>75250</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>60338</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>92213</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4089,12 +3023,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>61327</t>
+          <t>60338</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>92268</t>
+          <t>92213</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4104,47 +3038,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>75250</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>61327</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>92268</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>20,48%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>16,69%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>25,11%</t>
+          <t>25,09%</t>
         </is>
       </c>
     </row>
@@ -4157,37 +3056,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>304</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>292259</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>275296</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>307171</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>74,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4202,12 +3101,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>275241</t>
+          <t>275296</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>306182</t>
+          <t>307171</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4217,47 +3116,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>74,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>292259</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>275241</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>306182</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>79,52%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>74,89%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>83,31%</t>
+          <t>83,58%</t>
         </is>
       </c>
     </row>
@@ -4270,37 +3134,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>378</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>367509</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>367509</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>367509</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4334,41 +3198,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>378</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>367509</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>367509</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>367509</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4387,37 +3216,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>97</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>100175</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>84316</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>119386</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4432,12 +3261,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>83981</t>
+          <t>84316</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>117352</t>
+          <t>119386</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4447,47 +3276,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>100175</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>83981</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>117352</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>20,0%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>16,76%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>23,43%</t>
+          <t>23,83%</t>
         </is>
       </c>
     </row>
@@ -4500,37 +3294,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>404</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>400793</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>381582</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>416652</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>76,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4545,12 +3339,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>383616</t>
+          <t>381582</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>416987</t>
+          <t>416652</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4560,47 +3354,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,57%</t>
+          <t>76,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>400793</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>383616</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>416987</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>80,0%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>76,57%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>83,24%</t>
+          <t>83,17%</t>
         </is>
       </c>
     </row>
@@ -4613,37 +3372,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>501</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>500968</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>500968</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>500968</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4677,41 +3436,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>501</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>500968</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>500968</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>500968</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4730,37 +3454,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>71809</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56585</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>90953</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4775,12 +3499,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>57345</t>
+          <t>56585</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>89847</t>
+          <t>90953</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4790,47 +3514,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>71809</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>57345</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>89847</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>15,21%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>12,14%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>19,03%</t>
+          <t>19,26%</t>
         </is>
       </c>
     </row>
@@ -4843,37 +3532,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>372</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>400413</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>381269</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>415637</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4888,12 +3577,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>382375</t>
+          <t>381269</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>414877</t>
+          <t>415637</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4903,47 +3592,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>372</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>400413</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>382375</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>414877</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>84,79%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>80,97%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>87,86%</t>
+          <t>88,02%</t>
         </is>
       </c>
     </row>
@@ -4956,37 +3610,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>437</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>472222</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>472222</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>472222</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5020,41 +3674,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>437</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>472222</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>472222</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>472222</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5073,37 +3692,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>44954</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>33826</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>61066</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5118,12 +3737,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32807</t>
+          <t>33826</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>58730</t>
+          <t>61066</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5133,47 +3752,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>44954</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>32807</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>58730</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>14,01%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>10,23%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>18,31%</t>
+          <t>19,03%</t>
         </is>
       </c>
     </row>
@@ -5186,37 +3770,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>240</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>275874</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>259762</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>287002</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5231,12 +3815,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>262098</t>
+          <t>259762</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>288021</t>
+          <t>287002</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5246,47 +3830,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>275874</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>262098</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>288021</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>85,99%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>81,69%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>89,77%</t>
+          <t>89,46%</t>
         </is>
       </c>
     </row>
@@ -5299,37 +3848,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>278</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>320828</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>320828</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>320828</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5363,41 +3912,6 @@
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>278</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>320828</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>320828</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>320828</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5416,37 +3930,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>25172</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>16195</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>36279</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5461,12 +3975,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16768</t>
+          <t>16195</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>35949</t>
+          <t>36279</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5476,47 +3990,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>25172</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>16768</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>35949</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>12,45%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>8,29%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>17,78%</t>
+          <t>17,94%</t>
         </is>
       </c>
     </row>
@@ -5529,37 +4008,37 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>164</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>177040</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>165933</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>186017</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5574,12 +4053,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>166263</t>
+          <t>165933</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>185444</t>
+          <t>186017</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5589,47 +4068,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>177040</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>166263</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>185444</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>87,55%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>82,22%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>91,71%</t>
+          <t>91,99%</t>
         </is>
       </c>
     </row>
@@ -5642,37 +4086,37 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>187</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>202212</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>202212</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>202212</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5706,41 +4150,6 @@
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>202212</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>202212</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>202212</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5759,37 +4168,37 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10610</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4628</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21399</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5804,12 +4213,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4772</t>
+          <t>4628</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22189</t>
+          <t>21399</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5819,47 +4228,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>10610</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>4772</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>22189</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>8,18%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>3,68%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>17,1%</t>
+          <t>16,49%</t>
         </is>
       </c>
     </row>
@@ -5872,37 +4246,37 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>89</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>119167</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>108378</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>125149</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5917,12 +4291,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>107588</t>
+          <t>108378</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>125005</t>
+          <t>125149</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5932,47 +4306,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>119167</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>107588</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>125005</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>91,82%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>82,9%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>96,32%</t>
+          <t>96,43%</t>
         </is>
       </c>
     </row>
@@ -5985,37 +4324,37 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>96</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>129777</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>129777</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>129777</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6049,41 +4388,6 @@
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>129777</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>129777</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>129777</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6102,37 +4406,37 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>329</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>353039</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>319342</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>387366</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6147,12 +4451,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>321040</t>
+          <t>319342</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>390812</t>
+          <t>387366</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6162,47 +4466,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>329</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>353039</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>321040</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>390812</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>16,39%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>14,91%</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>18,15%</t>
+          <t>17,99%</t>
         </is>
       </c>
     </row>
@@ -6215,37 +4484,37 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1711</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1800635</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1766308</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1834332</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6260,12 +4529,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1762862</t>
+          <t>1766308</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1832634</t>
+          <t>1834332</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6275,47 +4544,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>1711</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>1800635</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>1762862</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>1832634</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>83,61%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>81,85%</t>
-        </is>
-      </c>
-      <c r="W26" s="2" t="inlineStr">
-        <is>
-          <t>85,09%</t>
+          <t>85,17%</t>
         </is>
       </c>
     </row>
@@ -6328,37 +4562,37 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2040</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2153674</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2153674</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2153674</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6392,41 +4626,6 @@
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>2040</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>2153674</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>2153674</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t>2153674</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W27" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6440,7 +4639,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="11">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -6449,7 +4648,6 @@
     <mergeCell ref="A25:A27"/>
     <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
@@ -6464,7 +4662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W28"/>
+  <dimension ref="A1:P28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6483,25 +4681,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el lugar donde le realizaron dicha citología vaginal en 2023</t>
+          <t>Población según si era asistencia pública o privada donde le realizaron la última citología vaginal en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6512,7 +4703,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6521,17 +4712,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -6602,41 +4782,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -6659,13 +4804,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -6680,37 +4818,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15668</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7873</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>24528</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>56,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6725,12 +4863,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7577</t>
+          <t>7873</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24526</t>
+          <t>24528</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6740,45 +4878,10 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>56,8%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>15668</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>7577</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>24526</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>36,28%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>17,55%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
         <is>
           <t>56,8%</t>
         </is>
@@ -6793,37 +4896,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>27513</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>18653</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>35308</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>63,72%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>43,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6838,12 +4941,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18655</t>
+          <t>18653</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35604</t>
+          <t>35308</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6858,42 +4961,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>27513</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>18655</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>35604</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>63,72%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>43,2%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>82,45%</t>
+          <t>81,77%</t>
         </is>
       </c>
     </row>
@@ -6906,37 +4974,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>43181</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>43181</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>43181</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6970,41 +5038,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>43181</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>43181</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>43181</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -7023,37 +5056,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>46018</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20539</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>71742</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7068,12 +5101,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17463</t>
+          <t>20539</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>71440</t>
+          <t>71742</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7083,47 +5116,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>46018</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>17463</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>71440</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>18,79%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>7,13%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>29,17%</t>
+          <t>29,29%</t>
         </is>
       </c>
     </row>
@@ -7136,37 +5134,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>127</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>198905</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>173181</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>224384</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>81,21%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7181,12 +5179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>173483</t>
+          <t>173181</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>227460</t>
+          <t>224384</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7196,47 +5194,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,83%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>198905</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>173483</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>227460</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>81,21%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>70,83%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>92,87%</t>
+          <t>91,61%</t>
         </is>
       </c>
     </row>
@@ -7249,37 +5212,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>171</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>244923</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>244923</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>244923</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7313,41 +5276,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>244923</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>244923</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>244923</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -7366,37 +5294,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>109</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>71599</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>60545</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>83953</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7411,12 +5339,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>60393</t>
+          <t>60545</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>84298</t>
+          <t>83953</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7426,47 +5354,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>71599</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>60393</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>84298</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>27,98%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>23,6%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>32,94%</t>
+          <t>32,81%</t>
         </is>
       </c>
     </row>
@@ -7479,37 +5372,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>285</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>184283</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>171929</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>195337</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>67,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>76,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7524,12 +5417,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>171584</t>
+          <t>171929</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>195489</t>
+          <t>195337</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7539,47 +5432,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,06%</t>
+          <t>67,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>184283</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>171584</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>195489</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>72,02%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>67,06%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>76,4%</t>
+          <t>76,34%</t>
         </is>
       </c>
     </row>
@@ -7592,37 +5450,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>394</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>255882</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>255882</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>255882</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7656,41 +5514,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>394</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>255882</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>255882</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>255882</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -7709,37 +5532,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>179</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>108430</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>75823</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>124261</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7754,12 +5577,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>77557</t>
+          <t>75823</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>125684</t>
+          <t>124261</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7769,47 +5592,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>108430</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>77557</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>125684</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>27,93%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>19,98%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>32,37%</t>
+          <t>32,01%</t>
         </is>
       </c>
     </row>
@@ -7822,37 +5610,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>408</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>279789</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>263958</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>312396</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>72,07%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>67,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7867,12 +5655,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>262535</t>
+          <t>263958</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>310662</t>
+          <t>312396</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7882,47 +5670,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,63%</t>
+          <t>67,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>408</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>279789</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>262535</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>310662</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>72,07%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>67,63%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>80,02%</t>
+          <t>80,47%</t>
         </is>
       </c>
     </row>
@@ -7935,37 +5688,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>587</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>388219</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>388219</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>388219</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7999,41 +5752,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>587</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>388219</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>388219</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>388219</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -8052,37 +5770,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>110</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>63086</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>53499</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>74529</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8097,12 +5815,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>54137</t>
+          <t>53499</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>74297</t>
+          <t>74529</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8112,47 +5830,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>63086</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>54137</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>74297</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>22,19%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>19,04%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>26,13%</t>
+          <t>26,21%</t>
         </is>
       </c>
     </row>
@@ -8165,37 +5848,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>406</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>221243</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>209800</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>230830</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8210,12 +5893,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>210032</t>
+          <t>209800</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>230192</t>
+          <t>230830</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8225,47 +5908,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>406</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>221243</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>210032</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>230192</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>77,81%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>73,87%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>80,96%</t>
+          <t>81,18%</t>
         </is>
       </c>
     </row>
@@ -8278,37 +5926,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>516</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>284329</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>284329</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>284329</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8342,41 +5990,6 @@
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>516</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>284329</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>284329</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>284329</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -8395,37 +6008,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>67</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>33765</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>26561</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>41828</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8440,12 +6053,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26402</t>
+          <t>26561</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41719</t>
+          <t>41828</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8455,47 +6068,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>33765</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>26402</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>41719</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>17,1%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>13,37%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>21,12%</t>
+          <t>21,18%</t>
         </is>
       </c>
     </row>
@@ -8508,37 +6086,37 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>338</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>163726</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>155663</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>170930</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8553,12 +6131,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>155772</t>
+          <t>155663</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>171089</t>
+          <t>170930</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8568,47 +6146,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,88%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>338</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>163726</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>155772</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>171089</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>82,9%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>78,88%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>86,63%</t>
+          <t>86,55%</t>
         </is>
       </c>
     </row>
@@ -8621,37 +6164,37 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>405</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>197491</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>197491</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>197491</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8685,41 +6228,6 @@
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>405</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>197491</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>197491</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>197491</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -8738,37 +6246,37 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>42</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21444</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15718</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>28908</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8783,12 +6291,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15762</t>
+          <t>15718</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>28342</t>
+          <t>28908</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8798,47 +6306,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>21444</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>15762</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>28342</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>13,68%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>10,06%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>18,08%</t>
+          <t>18,44%</t>
         </is>
       </c>
     </row>
@@ -8851,37 +6324,37 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>275</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>135284</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>127820</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>141010</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8896,12 +6369,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>128386</t>
+          <t>127820</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>140966</t>
+          <t>141010</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8911,47 +6384,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>135284</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>128386</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>140966</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>86,32%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>81,92%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>89,94%</t>
+          <t>89,97%</t>
         </is>
       </c>
     </row>
@@ -8964,37 +6402,37 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>317</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>156728</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>156728</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>156728</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9028,41 +6466,6 @@
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>317</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>156728</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>156728</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>156728</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9081,37 +6484,37 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>560</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>360010</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>301053</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>395733</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9126,12 +6529,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>301917</t>
+          <t>301053</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>392688</t>
+          <t>395733</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9141,47 +6544,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>560</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>360010</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>301917</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>392688</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>22,92%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>19,22%</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>25,0%</t>
+          <t>25,19%</t>
         </is>
       </c>
     </row>
@@ -9194,37 +6562,37 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1858</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1210742</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1175019</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1269699</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,08%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>74,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9239,12 +6607,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1178064</t>
+          <t>1175019</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1268835</t>
+          <t>1269699</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9254,47 +6622,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>74,81%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>1858</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>1210742</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>1178064</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>1268835</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>77,08%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>75,0%</t>
-        </is>
-      </c>
-      <c r="W26" s="2" t="inlineStr">
-        <is>
-          <t>80,78%</t>
+          <t>80,83%</t>
         </is>
       </c>
     </row>
@@ -9307,37 +6640,37 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2418</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1570752</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1570752</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1570752</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9371,41 +6704,6 @@
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>2418</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>1570752</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>1570752</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t>1570752</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W27" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9419,7 +6717,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="11">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -9428,7 +6726,6 @@
     <mergeCell ref="A25:A27"/>
     <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>

--- a/data/trans_orig/P43E-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P43E-Edad-trans_orig.xlsx
@@ -672,12 +672,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26173</t>
+          <t>26368</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47987</t>
+          <t>48393</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -687,12 +687,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26173</t>
+          <t>26368</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47987</t>
+          <t>48393</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>29,08%</t>
         </is>
       </c>
     </row>
@@ -750,12 +750,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>118426</t>
+          <t>118020</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>140240</t>
+          <t>140045</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -785,12 +785,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>118426</t>
+          <t>118020</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>140240</t>
+          <t>140045</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,16%</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>100056</t>
+          <t>100277</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>138245</t>
+          <t>137019</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -925,12 +925,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -945,12 +945,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>100056</t>
+          <t>100277</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>138245</t>
+          <t>137019</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,05%</t>
         </is>
       </c>
     </row>
@@ -988,12 +988,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>303108</t>
+          <t>304334</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>341297</t>
+          <t>341076</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1003,12 +1003,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1023,12 +1023,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>303108</t>
+          <t>304334</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>341297</t>
+          <t>341076</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,28%</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>129239</t>
+          <t>127906</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>174061</t>
+          <t>171514</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1163,12 +1163,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1183,12 +1183,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>129239</t>
+          <t>127906</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>174061</t>
+          <t>171514</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,15%</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>394869</t>
+          <t>397416</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>439691</t>
+          <t>441024</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>69,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>77,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1261,12 +1261,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>394869</t>
+          <t>397416</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>439691</t>
+          <t>441024</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1276,12 +1276,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>69,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>77,52%</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>95205</t>
+          <t>97166</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>139547</t>
+          <t>138808</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1401,12 +1401,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1421,12 +1421,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>95205</t>
+          <t>97166</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>139547</t>
+          <t>138808</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>28,76%</t>
         </is>
       </c>
     </row>
@@ -1464,12 +1464,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>343040</t>
+          <t>343779</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>387382</t>
+          <t>385421</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1479,12 +1479,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>71,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>343040</t>
+          <t>343779</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>387382</t>
+          <t>385421</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1514,12 +1514,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>71,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>79,87%</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>44868</t>
+          <t>43522</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>75543</t>
+          <t>73096</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1639,12 +1639,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>44868</t>
+          <t>43522</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>75543</t>
+          <t>73096</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>23,57%</t>
         </is>
       </c>
     </row>
@@ -1702,12 +1702,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>234544</t>
+          <t>236991</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>265219</t>
+          <t>266565</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1717,12 +1717,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1737,12 +1737,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>234544</t>
+          <t>236991</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>265219</t>
+          <t>266565</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1752,12 +1752,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,96%</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14004</t>
+          <t>13856</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32251</t>
+          <t>33599</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1877,12 +1877,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1897,12 +1897,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14004</t>
+          <t>13856</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>32251</t>
+          <t>33599</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1912,12 +1912,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,87%</t>
         </is>
       </c>
     </row>
@@ -1940,12 +1940,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>145757</t>
+          <t>144409</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>164004</t>
+          <t>164152</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1975,12 +1975,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>145757</t>
+          <t>144409</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>164004</t>
+          <t>164152</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1990,12 +1990,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,22%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7856</t>
+          <t>8538</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>22734</t>
+          <t>23886</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7856</t>
+          <t>8538</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22734</t>
+          <t>23886</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>23,5%</t>
         </is>
       </c>
     </row>
@@ -2178,12 +2178,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>78913</t>
+          <t>77761</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>93791</t>
+          <t>93109</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2193,12 +2193,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>76,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2213,12 +2213,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>78913</t>
+          <t>77761</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>93791</t>
+          <t>93109</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>76,5%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>91,6%</t>
         </is>
       </c>
     </row>
@@ -2338,12 +2338,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>474104</t>
+          <t>478474</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>558644</t>
+          <t>559306</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -2353,12 +2353,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>474104</t>
+          <t>478474</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>558644</t>
+          <t>559306</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2388,12 +2388,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,87%</t>
         </is>
       </c>
     </row>
@@ -2416,12 +2416,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1690381</t>
+          <t>1689719</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1774921</t>
+          <t>1770551</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2431,12 +2431,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>75,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1690381</t>
+          <t>1689719</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1774921</t>
+          <t>1770551</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2466,12 +2466,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>75,13%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>78,73%</t>
         </is>
       </c>
     </row>
@@ -2750,12 +2750,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17379</t>
+          <t>17244</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35268</t>
+          <t>36092</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2785,12 +2785,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17379</t>
+          <t>17244</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35268</t>
+          <t>36092</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2800,12 +2800,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,54%</t>
         </is>
       </c>
     </row>
@@ -2828,12 +2828,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>124891</t>
+          <t>124067</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>142780</t>
+          <t>142915</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>77,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>124891</t>
+          <t>124067</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>142780</t>
+          <t>142915</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>77,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,23%</t>
         </is>
       </c>
     </row>
@@ -2988,12 +2988,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>60338</t>
+          <t>61491</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>92213</t>
+          <t>92136</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3003,12 +3003,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>60338</t>
+          <t>61491</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>92213</t>
+          <t>92136</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,07%</t>
         </is>
       </c>
     </row>
@@ -3066,12 +3066,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>275296</t>
+          <t>275373</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>307171</t>
+          <t>306018</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3081,12 +3081,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>275296</t>
+          <t>275373</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>307171</t>
+          <t>306018</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,27%</t>
         </is>
       </c>
     </row>
@@ -3226,12 +3226,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>84316</t>
+          <t>83303</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>119386</t>
+          <t>117802</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3241,12 +3241,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>84316</t>
+          <t>83303</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>119386</t>
+          <t>117802</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3276,12 +3276,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,51%</t>
         </is>
       </c>
     </row>
@@ -3304,12 +3304,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>381582</t>
+          <t>383166</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>416652</t>
+          <t>417665</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>83,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3339,12 +3339,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>381582</t>
+          <t>383166</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>416652</t>
+          <t>417665</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3354,12 +3354,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>83,37%</t>
         </is>
       </c>
     </row>
@@ -3464,12 +3464,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>56585</t>
+          <t>56638</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>90953</t>
+          <t>90131</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3479,12 +3479,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>56585</t>
+          <t>56638</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>90953</t>
+          <t>90131</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,09%</t>
         </is>
       </c>
     </row>
@@ -3542,12 +3542,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>381269</t>
+          <t>382091</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>415637</t>
+          <t>415584</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3557,12 +3557,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3577,12 +3577,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>381269</t>
+          <t>382091</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>415637</t>
+          <t>415584</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3592,12 +3592,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>88,01%</t>
         </is>
       </c>
     </row>
@@ -3702,12 +3702,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33826</t>
+          <t>32484</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>61066</t>
+          <t>58724</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -3717,12 +3717,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>33826</t>
+          <t>32484</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>61066</t>
+          <t>58724</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -3752,12 +3752,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,3%</t>
         </is>
       </c>
     </row>
@@ -3780,12 +3780,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>259762</t>
+          <t>262104</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>287002</t>
+          <t>288344</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>259762</t>
+          <t>262104</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>287002</t>
+          <t>288344</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -3830,12 +3830,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,88%</t>
         </is>
       </c>
     </row>
@@ -3940,12 +3940,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16195</t>
+          <t>16374</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>36279</t>
+          <t>36286</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16195</t>
+          <t>16374</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>36279</t>
+          <t>36286</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -3990,7 +3990,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -4018,12 +4018,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>165933</t>
+          <t>165926</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>186017</t>
+          <t>185838</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>165933</t>
+          <t>165926</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>186017</t>
+          <t>185838</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>91,9%</t>
         </is>
       </c>
     </row>
@@ -4178,12 +4178,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4628</t>
+          <t>4928</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21399</t>
+          <t>20422</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4628</t>
+          <t>4928</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21399</t>
+          <t>20422</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>15,74%</t>
         </is>
       </c>
     </row>
@@ -4256,12 +4256,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>108378</t>
+          <t>109355</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>125149</t>
+          <t>124849</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -4271,12 +4271,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -4291,12 +4291,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>108378</t>
+          <t>109355</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>125149</t>
+          <t>124849</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,2%</t>
         </is>
       </c>
     </row>
@@ -4416,12 +4416,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>319342</t>
+          <t>318740</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>387366</t>
+          <t>387912</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>319342</t>
+          <t>318740</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>387366</t>
+          <t>387912</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,01%</t>
         </is>
       </c>
     </row>
@@ -4494,12 +4494,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1766308</t>
+          <t>1765762</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1834332</t>
+          <t>1834934</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1766308</t>
+          <t>1765762</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1834332</t>
+          <t>1834934</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>85,2%</t>
         </is>
       </c>
     </row>
@@ -4823,32 +4823,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>15668</t>
+          <t>15562</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7873</t>
+          <t>7714</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24528</t>
+          <t>25569</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>53,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4858,32 +4858,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>15668</t>
+          <t>15562</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7873</t>
+          <t>7714</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24528</t>
+          <t>25569</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>53,35%</t>
         </is>
       </c>
     </row>
@@ -4901,32 +4901,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>27513</t>
+          <t>32363</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18653</t>
+          <t>22356</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35308</t>
+          <t>40211</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>46,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4936,32 +4936,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>27513</t>
+          <t>32363</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18653</t>
+          <t>22356</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35308</t>
+          <t>40211</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>46,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>83,9%</t>
         </is>
       </c>
     </row>
@@ -4979,17 +4979,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>43181</t>
+          <t>47925</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>43181</t>
+          <t>47925</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>43181</t>
+          <t>47925</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5014,17 +5014,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>43181</t>
+          <t>47925</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>43181</t>
+          <t>47925</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>43181</t>
+          <t>47925</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5061,32 +5061,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>46018</t>
+          <t>51235</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20539</t>
+          <t>37755</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>71742</t>
+          <t>64648</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5096,32 +5096,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>46018</t>
+          <t>51235</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20539</t>
+          <t>37755</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>71742</t>
+          <t>64648</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>33,75%</t>
         </is>
       </c>
     </row>
@@ -5139,32 +5139,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>198905</t>
+          <t>140309</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>173181</t>
+          <t>126896</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>224384</t>
+          <t>153789</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>81,21%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>66,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5174,32 +5174,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>198905</t>
+          <t>140309</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>173181</t>
+          <t>126896</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>224384</t>
+          <t>153789</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>81,21%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>66,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>80,29%</t>
         </is>
       </c>
     </row>
@@ -5217,17 +5217,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>244923</t>
+          <t>191544</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>244923</t>
+          <t>191544</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>244923</t>
+          <t>191544</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5252,17 +5252,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>244923</t>
+          <t>191544</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>244923</t>
+          <t>191544</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>244923</t>
+          <t>191544</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5299,32 +5299,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>71599</t>
+          <t>79806</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>60545</t>
+          <t>67157</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>83953</t>
+          <t>93027</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5334,32 +5334,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>71599</t>
+          <t>79806</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>60545</t>
+          <t>67157</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>83953</t>
+          <t>93027</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,1%</t>
         </is>
       </c>
     </row>
@@ -5377,32 +5377,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>184283</t>
+          <t>210003</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>171929</t>
+          <t>196782</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>195337</t>
+          <t>222652</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>67,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,34%</t>
+          <t>76,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5412,32 +5412,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>184283</t>
+          <t>210003</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>171929</t>
+          <t>196782</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>195337</t>
+          <t>222652</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>67,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,34%</t>
+          <t>76,83%</t>
         </is>
       </c>
     </row>
@@ -5455,17 +5455,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>255882</t>
+          <t>289809</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>255882</t>
+          <t>289809</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>255882</t>
+          <t>289809</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5490,17 +5490,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>255882</t>
+          <t>289809</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>255882</t>
+          <t>289809</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>255882</t>
+          <t>289809</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>108430</t>
+          <t>117955</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>75823</t>
+          <t>104172</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>124261</t>
+          <t>132463</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>108430</t>
+          <t>117955</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>75823</t>
+          <t>104172</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>124261</t>
+          <t>132463</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>34,79%</t>
         </is>
       </c>
     </row>
@@ -5615,32 +5615,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>279789</t>
+          <t>262848</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>263958</t>
+          <t>248340</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>312396</t>
+          <t>276631</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>72,07%</t>
+          <t>69,02%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,99%</t>
+          <t>65,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5650,32 +5650,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>279789</t>
+          <t>262848</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>263958</t>
+          <t>248340</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>312396</t>
+          <t>276631</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>72,07%</t>
+          <t>69,02%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,99%</t>
+          <t>65,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>72,64%</t>
         </is>
       </c>
     </row>
@@ -5693,17 +5693,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>388219</t>
+          <t>380803</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>388219</t>
+          <t>380803</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>388219</t>
+          <t>380803</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5728,17 +5728,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>388219</t>
+          <t>380803</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>388219</t>
+          <t>380803</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>388219</t>
+          <t>380803</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5775,32 +5775,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>63086</t>
+          <t>69735</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>53499</t>
+          <t>58691</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>74529</t>
+          <t>82278</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5810,32 +5810,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>63086</t>
+          <t>69735</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>53499</t>
+          <t>58691</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>74529</t>
+          <t>82278</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,19%</t>
         </is>
       </c>
     </row>
@@ -5853,32 +5853,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>221243</t>
+          <t>244366</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>209800</t>
+          <t>231823</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>230830</t>
+          <t>255410</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>77,8%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>81,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5888,32 +5888,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>221243</t>
+          <t>244366</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>209800</t>
+          <t>231823</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>230830</t>
+          <t>255410</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>77,8%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>81,31%</t>
         </is>
       </c>
     </row>
@@ -5931,17 +5931,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>284329</t>
+          <t>314101</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>284329</t>
+          <t>314101</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>284329</t>
+          <t>314101</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5966,17 +5966,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>284329</t>
+          <t>314101</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>284329</t>
+          <t>314101</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>284329</t>
+          <t>314101</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6013,32 +6013,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>33765</t>
+          <t>37303</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26561</t>
+          <t>29792</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>41828</t>
+          <t>45591</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6048,32 +6048,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>33765</t>
+          <t>37303</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26561</t>
+          <t>29792</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41828</t>
+          <t>45591</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,14%</t>
         </is>
       </c>
     </row>
@@ -6091,32 +6091,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>163726</t>
+          <t>178398</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>155663</t>
+          <t>170110</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>170930</t>
+          <t>185909</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>78,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6126,32 +6126,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>163726</t>
+          <t>178398</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>155663</t>
+          <t>170110</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>170930</t>
+          <t>185909</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>78,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,19%</t>
         </is>
       </c>
     </row>
@@ -6169,17 +6169,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>197491</t>
+          <t>215701</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>197491</t>
+          <t>215701</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>197491</t>
+          <t>215701</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6204,17 +6204,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>197491</t>
+          <t>215701</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>197491</t>
+          <t>215701</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>197491</t>
+          <t>215701</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6251,32 +6251,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>21444</t>
+          <t>23608</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15718</t>
+          <t>17716</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28908</t>
+          <t>30850</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6286,32 +6286,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>21444</t>
+          <t>23608</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15718</t>
+          <t>17716</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>28908</t>
+          <t>30850</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,19%</t>
         </is>
       </c>
     </row>
@@ -6329,32 +6329,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>135284</t>
+          <t>146022</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>127820</t>
+          <t>138780</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>141010</t>
+          <t>151914</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6364,32 +6364,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>135284</t>
+          <t>146022</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>127820</t>
+          <t>138780</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>141010</t>
+          <t>151914</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>89,56%</t>
         </is>
       </c>
     </row>
@@ -6407,17 +6407,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>156728</t>
+          <t>169630</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>156728</t>
+          <t>169630</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>156728</t>
+          <t>169630</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6442,17 +6442,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>156728</t>
+          <t>169630</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>156728</t>
+          <t>169630</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>156728</t>
+          <t>169630</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6489,32 +6489,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>360010</t>
+          <t>395204</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>301053</t>
+          <t>365309</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>395733</t>
+          <t>424889</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6524,32 +6524,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>360010</t>
+          <t>395204</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>301053</t>
+          <t>365309</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>395733</t>
+          <t>424889</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>26,4%</t>
         </is>
       </c>
     </row>
@@ -6567,32 +6567,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1210742</t>
+          <t>1214309</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1175019</t>
+          <t>1184624</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1269699</t>
+          <t>1244204</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>75,45%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>73,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>77,3%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6602,32 +6602,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1210742</t>
+          <t>1214309</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1175019</t>
+          <t>1184624</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1269699</t>
+          <t>1244204</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>75,45%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>73,6%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>77,3%</t>
         </is>
       </c>
     </row>
@@ -6645,17 +6645,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1570752</t>
+          <t>1609513</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1570752</t>
+          <t>1609513</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1570752</t>
+          <t>1609513</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6680,17 +6680,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1570752</t>
+          <t>1609513</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1570752</t>
+          <t>1609513</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1570752</t>
+          <t>1609513</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
